--- a/TPO/2/Testing check-list for Lab-2.xlsx
+++ b/TPO/2/Testing check-list for Lab-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Labs_6\TPO\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7E5FBD-39ED-4F35-8416-0D23CC71E6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D705D5A-4149-4057-BBE7-17AD51166858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conformance testing - Android" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="158">
   <si>
     <t>Conformance testing check-list (Android)</t>
   </si>
@@ -447,6 +447,72 @@
   </si>
   <si>
     <t>СТ-65</t>
+  </si>
+  <si>
+    <t>Просмотр личного кабинета</t>
+  </si>
+  <si>
+    <t>Просмотр истории в личном кабинете</t>
+  </si>
+  <si>
+    <t>Корректное обновление истории в личном кабинете</t>
+  </si>
+  <si>
+    <t>Просмотр номера телефона</t>
+  </si>
+  <si>
+    <t>Изменение номера телефона</t>
+  </si>
+  <si>
+    <t>Просмотр имени</t>
+  </si>
+  <si>
+    <t>Изменение имени</t>
+  </si>
+  <si>
+    <t>Просмтор логина</t>
+  </si>
+  <si>
+    <t>Изменение логина</t>
+  </si>
+  <si>
+    <t>Просмотр пароля</t>
+  </si>
+  <si>
+    <t>Изменение пароля</t>
+  </si>
+  <si>
+    <t>Просмотр пользователей</t>
+  </si>
+  <si>
+    <t>Добавление пользователей</t>
+  </si>
+  <si>
+    <t>Изменение пользователей</t>
+  </si>
+  <si>
+    <t>Блокировка пользователей</t>
+  </si>
+  <si>
+    <t>Нельзя ли заблокирлвать администратора</t>
+  </si>
+  <si>
+    <t>Множественное бронирование</t>
+  </si>
+  <si>
+    <t>Начисление бонусов при отказе</t>
+  </si>
+  <si>
+    <t>Добавить велосипед</t>
+  </si>
+  <si>
+    <t>Изменить велосипед</t>
+  </si>
+  <si>
+    <t>Удалить велосипед</t>
+  </si>
+  <si>
+    <t>Просмотреть велосипеды</t>
   </si>
 </sst>
 </file>
@@ -698,7 +764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -768,6 +834,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -779,11 +850,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -793,6 +859,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1211,29 +1278,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="42" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="42" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1242,20 +1309,20 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="40"/>
+      <c r="E3" s="37"/>
       <c r="F3" s="20" t="str">
         <f>HYPERLINK("https://learn.microsoft.com/ru-ru/windows/apps/get-started/best-practices","Разработка приложений Windows — рекомендации")</f>
         <v>Разработка приложений Windows — рекомендации</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="35" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="25" t="s">
@@ -1271,7 +1338,7 @@
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="25" t="s">
         <v>10</v>
       </c>
@@ -1284,7 +1351,7 @@
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="41"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="25" t="s">
         <v>11</v>
       </c>
@@ -1292,12 +1359,12 @@
         <v>62</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="25" t="s">
         <v>12</v>
       </c>
@@ -1310,7 +1377,7 @@
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="41"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="25" t="s">
         <v>13</v>
       </c>
@@ -1323,7 +1390,7 @@
       <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="41"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="25" t="s">
         <v>14</v>
       </c>
@@ -1336,7 +1403,7 @@
       <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="41"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="25" t="s">
         <v>15</v>
       </c>
@@ -1349,7 +1416,7 @@
       <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="25" t="s">
         <v>16</v>
       </c>
@@ -1362,7 +1429,7 @@
       <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="35" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="25" t="s">
@@ -1377,7 +1444,7 @@
       <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="41"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="25" t="s">
         <v>18</v>
       </c>
@@ -1390,7 +1457,7 @@
       <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="41"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="7" t="s">
         <v>19</v>
       </c>
@@ -1398,12 +1465,12 @@
         <v>70</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="41"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1411,12 +1478,12 @@
         <v>71</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="40"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="7" t="s">
         <v>21</v>
       </c>
@@ -1424,12 +1491,12 @@
         <v>72</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="35" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -1470,7 +1537,7 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="35" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="25" t="s">
@@ -1485,7 +1552,7 @@
       <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="41"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="25" t="s">
         <v>24</v>
       </c>
@@ -1498,7 +1565,7 @@
       <c r="E21" s="30"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="41"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="25" t="s">
         <v>25</v>
       </c>
@@ -1511,7 +1578,7 @@
       <c r="E22" s="31"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="41"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="25" t="s">
         <v>26</v>
       </c>
@@ -1524,7 +1591,7 @@
       <c r="E23" s="32"/>
     </row>
     <row r="24" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="41"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="25" t="s">
         <v>27</v>
       </c>
@@ -1537,7 +1604,7 @@
       <c r="E24" s="32"/>
     </row>
     <row r="25" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="41"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="25" t="s">
         <v>28</v>
       </c>
@@ -1550,7 +1617,7 @@
       <c r="E25" s="32"/>
     </row>
     <row r="26" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="41"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="25" t="s">
         <v>29</v>
       </c>
@@ -1588,7 +1655,7 @@
         <v>108</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E28" s="34"/>
     </row>
@@ -1664,7 +1731,7 @@
       <c r="E33" s="34"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="35" t="s">
         <v>78</v>
       </c>
       <c r="B34" s="25" t="s">
@@ -1679,7 +1746,7 @@
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="41"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="25" t="s">
         <v>38</v>
       </c>
@@ -1692,7 +1759,7 @@
       <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="41"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="25" t="s">
         <v>39</v>
       </c>
@@ -1705,7 +1772,7 @@
       <c r="E36" s="10"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="41"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="25" t="s">
         <v>40</v>
       </c>
@@ -1718,7 +1785,7 @@
       <c r="E37" s="10"/>
     </row>
     <row r="38" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A38" s="40"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="25" t="s">
         <v>114</v>
       </c>
@@ -1731,7 +1798,7 @@
       <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="42" t="s">
+      <c r="A39" s="35" t="s">
         <v>59</v>
       </c>
       <c r="B39" s="25" t="s">
@@ -1865,251 +1932,296 @@
       <c r="E48" s="32"/>
     </row>
     <row r="49" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="38" t="s">
         <v>104</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="8"/>
+      <c r="C49" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="D49" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E49" s="32"/>
     </row>
     <row r="50" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A50" s="35"/>
+      <c r="A50" s="38"/>
       <c r="B50" s="25" t="s">
         <v>115</v>
       </c>
+      <c r="C50" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="D50" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E50" s="32"/>
     </row>
     <row r="51" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="35"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="C51" s="22"/>
+      <c r="C51" s="22" t="s">
+        <v>138</v>
+      </c>
       <c r="D51" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E51" s="32"/>
     </row>
     <row r="52" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35"/>
+      <c r="A52" s="38"/>
       <c r="B52" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="24"/>
+      <c r="C52" s="46" t="s">
+        <v>139</v>
+      </c>
       <c r="D52" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E52" s="32"/>
     </row>
     <row r="53" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A53" s="35"/>
+      <c r="A53" s="38"/>
       <c r="B53" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C53" s="24"/>
+      <c r="C53" s="46" t="s">
+        <v>140</v>
+      </c>
       <c r="D53" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E53" s="32"/>
     </row>
     <row r="54" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A54" s="35"/>
+      <c r="A54" s="38"/>
       <c r="B54" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="24"/>
+      <c r="C54" s="46" t="s">
+        <v>141</v>
+      </c>
       <c r="D54" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E54" s="32"/>
     </row>
     <row r="55" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A55" s="35"/>
+      <c r="A55" s="38"/>
       <c r="B55" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="24"/>
+      <c r="C55" s="46" t="s">
+        <v>142</v>
+      </c>
       <c r="D55" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E55" s="32"/>
     </row>
     <row r="56" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A56" s="35"/>
+      <c r="A56" s="38"/>
       <c r="B56" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="24"/>
+      <c r="C56" s="46" t="s">
+        <v>143</v>
+      </c>
       <c r="D56" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E56" s="32"/>
     </row>
     <row r="57" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="38" t="s">
         <v>104</v>
       </c>
       <c r="B57" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="C57" s="23"/>
+      <c r="C57" s="46" t="s">
+        <v>144</v>
+      </c>
       <c r="D57" s="33" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E57" s="32"/>
     </row>
     <row r="58" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A58" s="35"/>
+      <c r="A58" s="38"/>
       <c r="B58" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="11"/>
+      <c r="C58" s="46" t="s">
+        <v>145</v>
+      </c>
       <c r="D58" s="33" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E58" s="32"/>
     </row>
     <row r="59" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A59" s="35"/>
+      <c r="A59" s="38"/>
       <c r="B59" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="11"/>
+      <c r="C59" s="46" t="s">
+        <v>146</v>
+      </c>
       <c r="D59" s="33" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E59" s="32"/>
     </row>
     <row r="60" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A60" s="35"/>
+      <c r="A60" s="38"/>
       <c r="B60" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="11"/>
+      <c r="C60" s="11" t="s">
+        <v>157</v>
+      </c>
       <c r="D60" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E60" s="32"/>
     </row>
     <row r="61" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A61" s="35"/>
+      <c r="A61" s="38"/>
       <c r="B61" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C61" s="11"/>
+      <c r="C61" s="23" t="s">
+        <v>154</v>
+      </c>
       <c r="D61" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E61" s="32"/>
     </row>
     <row r="62" spans="1:5" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="38" t="s">
         <v>104</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="C62" s="11"/>
+      <c r="C62" s="11" t="s">
+        <v>155</v>
+      </c>
       <c r="D62" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E62" s="32"/>
     </row>
     <row r="63" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A63" s="35"/>
+      <c r="A63" s="38"/>
       <c r="B63" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C63" s="11"/>
+      <c r="C63" s="11" t="s">
+        <v>156</v>
+      </c>
       <c r="D63" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E63" s="32"/>
     </row>
     <row r="64" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A64" s="35"/>
+      <c r="A64" s="38"/>
       <c r="B64" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="11"/>
+      <c r="C64" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="D64" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E64" s="32"/>
     </row>
     <row r="65" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="35"/>
+      <c r="A65" s="38"/>
       <c r="B65" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="11"/>
+      <c r="C65" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="D65" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E65" s="32"/>
     </row>
     <row r="66" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A66" s="35"/>
+      <c r="A66" s="38"/>
       <c r="B66" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C66" s="11"/>
+      <c r="C66" s="11" t="s">
+        <v>149</v>
+      </c>
       <c r="D66" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E66" s="32"/>
     </row>
     <row r="67" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="35" t="s">
+      <c r="A67" s="38" t="s">
         <v>104</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="11"/>
+      <c r="C67" s="11" t="s">
+        <v>150</v>
+      </c>
       <c r="D67" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E67" s="32"/>
     </row>
     <row r="68" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="35"/>
+      <c r="A68" s="38"/>
       <c r="B68" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="11"/>
+      <c r="C68" s="11" t="s">
+        <v>151</v>
+      </c>
       <c r="D68" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E68" s="32"/>
     </row>
     <row r="69" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="35"/>
+      <c r="A69" s="38"/>
       <c r="B69" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="11"/>
+      <c r="C69" s="11" t="s">
+        <v>152</v>
+      </c>
       <c r="D69" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E69" s="32"/>
     </row>
     <row r="70" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="35"/>
+      <c r="A70" s="38"/>
       <c r="B70" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="C70" s="8"/>
+      <c r="C70" s="11" t="s">
+        <v>153</v>
+      </c>
       <c r="D70" s="33" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E70" s="32"/>
     </row>
@@ -2118,7 +2230,7 @@
         <v>52</v>
       </c>
       <c r="D71" s="13">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -2126,7 +2238,7 @@
         <v>53</v>
       </c>
       <c r="D72" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -2142,7 +2254,7 @@
         <v>55</v>
       </c>
       <c r="D74" s="13">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -4687,6 +4799,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A20:A26"/>
     <mergeCell ref="A34:A38"/>
     <mergeCell ref="A62:A66"/>
     <mergeCell ref="A67:A70"/>
@@ -4703,7 +4816,6 @@
     <mergeCell ref="A49:A56"/>
     <mergeCell ref="A44:A48"/>
     <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A20:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D70 C73:C75">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Not tested">
